--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-flagalert.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-flagalert.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-18T10:23:29+00:00</t>
+    <t>2026-01-28T10:05:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -567,7 +567,7 @@
     <t>Flag.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|Location|Group|Organization|Practitioner|PlanDefinition|Medication|Procedure)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|Location|Group|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|PlanDefinition|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medication|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-procedure)
 </t>
   </si>
   <si>
@@ -618,7 +618,7 @@
     <t>Flag.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-device|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole)
 </t>
   </si>
   <si>
@@ -954,7 +954,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="121.8203125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-flagalert.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-flagalert.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T10:05:57+00:00</t>
+    <t>2026-01-29T06:33:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-flagalert.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-flagalert.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T06:33:09+00:00</t>
+    <t>2026-02-03T10:06:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-flagalert.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-flagalert.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:06:44+00:00</t>
+    <t>2026-02-03T10:34:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-flagalert.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-flagalert.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:34:36+00:00</t>
+    <t>2026-02-09T07:50:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-flagalert.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-flagalert.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T07:50:08+00:00</t>
+    <t>2026-02-13T12:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-flagalert.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-flagalert.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T12:44:21+00:00</t>
+    <t>2026-02-16T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-flagalert.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-flagalert.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T08:31:54+00:00</t>
+    <t>2026-02-16T11:13:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-flagalert.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-flagalert.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T11:13:42+00:00</t>
+    <t>2026-02-17T09:00:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-flagalert.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-flagalert.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T09:00:43+00:00</t>
+    <t>2026-09-01T07:40:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
